--- a/01_藥物筆記/藥物資料庫.xlsx
+++ b/01_藥物筆記/藥物資料庫.xlsx
@@ -21,36 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">動物體重 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(kg)</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+  <si>
+    <t xml:space="preserve">動物體重 (kg)：</t>
   </si>
   <si>
     <t xml:space="preserve">＊藍色字＝可自行修改；輸入體重後，下方「計算劑量」欄會自動更新</t>
@@ -65,50 +38,10 @@
     <t xml:space="preserve">適用情境</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">劑量下限</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(mg/kg)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">劑量上限</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(mg/kg)</t>
-    </r>
+    <t xml:space="preserve">劑量下限(mg/kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">劑量上限(mg/kg)</t>
   </si>
   <si>
     <t xml:space="preserve">給藥途徑</t>
@@ -117,50 +50,10 @@
     <t xml:space="preserve">頻率</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計算劑量下限</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(mg)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計算劑量上限</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(mg)</t>
-    </r>
+    <t xml:space="preserve">計算劑量下限(mg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計算劑量上限(mg)</t>
   </si>
   <si>
     <t xml:space="preserve">禁忌與副作用</t>
@@ -172,6 +65,576 @@
     <t xml:space="preserve">Carprofen</t>
   </si>
   <si>
+    <t xml:space="preserve">止痛(NSAID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">門診/術後</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO/SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SID-BID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">禁用於腎/肝功能不全、GI潰瘍病史動物；避免與類固醇併用</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">門診用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Carprofen.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Meloxicam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">貓需嚴格依體重給藥，長期使用需監控腎功能</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">門診用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Meloxicam.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Buprenorphine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">止痛(鴉片類)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手術/住院</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IV/IM/SC/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頰黏膜</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TID-QID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼吸抑制風險，需監測</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手術麻醉用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Buprenorphine.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Amoxicillin-Clavulanate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抗生素</t>
+  </si>
+  <si>
+    <t xml:space="preserve">門診/住院</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">禁用於已知盤尼西林過敏動物</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">門診用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Amoxicillin-Clavulanate.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Cefazolin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抗生素(手術預防性)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手術</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">術前30分鐘, 術中每90分鐘追加</t>
+  </si>
+  <si>
+    <t xml:space="preserve">腎功能不全需調整劑量</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手術麻醉用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Cefazolin.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Maropitant (Cerenia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">止吐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC/PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小於16週齡幼犬貓避免使用</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">住院用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Maropitant.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dexmedetomidine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鎮靜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手術麻醉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV/IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">單次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">心血管疾病動物慎用，會造成心搏過緩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手術麻醉用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Dexmedetomidine.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Furosemide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">利尿劑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住院</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV/IM/PO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BID-QID (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">急性可更頻繁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">注意電解質流失、脫水</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">住院用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Furosemide.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Fentanyl</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -187,21 +650,208 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(NSAID)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">門診</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鴉片類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">麻醉前用藥</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手術麻醉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Premed)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">單次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(premed)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">另計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-10 mcg/kg/h(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">犬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-4 mcg/kg/h(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">貓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">呼吸抑制、心搏過緩風險；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">速率非本欄計算範圍，需另外換算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -210,31 +860,17 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">術後</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">PO/SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SID-BID</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">禁用於腎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依類別用藥筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -244,27 +880,151 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">肝功能不全、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">潰瘍病史動物；避免與類固醇併用</t>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止痛用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Fentanyl.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Midazolam</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鎮靜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">苯二氮平類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">麻醉前用藥</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">IV/IM/SC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">單次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(premed)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">opioid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">併用做</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">neuroleptanalgesia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；可用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Flumazenil 0.01 mg/kg IV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逆轉</t>
     </r>
   </si>
   <si>
@@ -304,27 +1064,255 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">門診用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Carprofen.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Meloxicam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">貓需嚴格依體重給藥，長期使用需監控腎功能</t>
+      <t xml:space="preserve">依類別用藥筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止痛用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Midazolam.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Alfaxalone (Alfaxan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻醉誘導劑</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手術麻醉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Induction)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IV(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">緩慢推注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,&gt;60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">單次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誘導</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">犬：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">premed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2mg/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、未</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">premed 3mg/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；貓：約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5mg/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；個體差異大，需 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">to effect </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">給藥，年老</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重症動物酌減</t>
+    </r>
   </si>
   <si>
     <r>
@@ -363,70 +1351,12 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">門診用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Meloxicam.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Buprenorphine</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止痛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鴉片類</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t xml:space="preserve">依類別用藥筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -435,37 +1365,158 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">住院</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IV/IM/SC/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頰黏膜</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TID-QID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呼吸抑制風險，需監測</t>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止痛用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Alfaxalone.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Isoflurane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吸入性麻醉維持</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手術麻醉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Maintenance)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">吸入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">持續</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⚠非</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mg/kg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">劑量，以吸入濃度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(vol%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">給予：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MAC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">犬約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／貓約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；維持濃度約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5-2.5%</t>
+    </r>
   </si>
   <si>
     <r>
@@ -504,37 +1555,12 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">手術麻醉用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Buprenorphine.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Amoxicillin-Clavulanate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">抗生素</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">門診</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t xml:space="preserve">依類別用藥筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -543,476 +1569,22 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">住院</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">禁用於已知盤尼西林過敏動物</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">門診用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Amoxicillin-Clavulanate.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Cefazolin</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">抗生素</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術預防性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">手術</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">術前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分鐘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">術中每</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分鐘追加</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">腎功能不全需調整劑量</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術麻醉用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Cefazolin.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Maropitant (Cerenia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">止吐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC/PO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小於</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週齡幼犬貓避免使用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">住院用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Maropitant.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Dexmedetomidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鎮靜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手術麻醉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV/IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">單次</t>
-  </si>
-  <si>
-    <t xml:space="preserve">心血管疾病動物慎用，會造成心搏過緩</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術麻醉用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Dexmedetomidine.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Furosemide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">利尿劑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">住院</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV/IM/PO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BID-QID (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">急性可更頻繁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">注意電解質流失、脫水</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">住院用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Furosemide.md</t>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止痛用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Isoflurane.md</t>
     </r>
   </si>
   <si>
@@ -1305,9 +1877,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00&quot; mg&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot; mg&quot;"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -1337,12 +1910,6 @@
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1359,6 +1926,7 @@
       <color rgb="FF808080"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1366,13 +1934,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1385,6 +1946,7 @@
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1397,11 +1959,6 @@
       <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1418,10 +1975,27 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="13"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1493,56 +2067,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1798,360 +2388,508 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="32"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="n">
+      <c r="B1" s="3" t="n">
         <v>4.5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>4.4</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <f aca="false">$B$1*D5</f>
         <v>9</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <f aca="false">$B$1*E5</f>
         <v>19.8</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <f aca="false">$B$1*D6</f>
         <v>0.225</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <f aca="false">$B$1*E6</f>
         <v>0.45</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>0.01</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>0.02</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <f aca="false">$B$1*D7</f>
         <v>0.045</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <f aca="false">$B$1*E7</f>
         <v>0.09</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <f aca="false">$B$1*D8</f>
         <v>56.25</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <f aca="false">$B$1*E8</f>
         <v>112.5</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <f aca="false">$B$1*D9</f>
         <v>99</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <f aca="false">$B$1*E9</f>
         <v>99</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="9" t="n">
         <f aca="false">$B$1*D10</f>
         <v>4.5</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="9" t="n">
         <f aca="false">$B$1*E10</f>
         <v>4.5</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>0.005</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>0.01</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="9" t="n">
         <f aca="false">$B$1*D11</f>
         <v>0.0225</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="9" t="n">
         <f aca="false">$B$1*E11</f>
         <v>0.045</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="9" t="n">
         <f aca="false">$B$1*D12</f>
         <v>4.5</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="9" t="n">
         <f aca="false">$B$1*E12</f>
         <v>9</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="11" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <f aca="false">$B$1*D13</f>
+        <v>0.009</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <f aca="false">$B$1*E13</f>
+        <v>0.0225</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <f aca="false">$B$1*D14</f>
+        <v>0.45</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <f aca="false">$B$1*E14</f>
+        <v>1.8</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <f aca="false">$B$1*D15</f>
+        <v>4.5</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <f aca="false">$B$1*E15</f>
+        <v>22.5</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <f aca="false">$B$1*D16</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <f aca="false">$B$1*E16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2173,40 +2911,40 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="100"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>64</v>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12"/>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16"/>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>65</v>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>66</v>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>67</v>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>68</v>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>69</v>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/01_藥物筆記/藥物資料庫.xlsx
+++ b/01_藥物筆記/藥物資料庫.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
   <si>
     <t xml:space="preserve">動物體重 (kg)：</t>
   </si>
@@ -635,127 +635,213 @@
     <t xml:space="preserve">Fentanyl</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止痛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鴉片類</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">麻醉前用藥</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術麻醉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Premed)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單次</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(premed)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">另計 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2-10 mcg/kg/h(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">犬</t>
+    <t xml:space="preserve">止痛(鴉片類)/麻醉前用藥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手術麻醉(Premed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">單次(premed)；CRI另計 2-10 mcg/kg/h(犬)、1-4 mcg/kg/h(貓)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呼吸抑制、心搏過緩風險；CRI速率非本欄計算範圍，需另外換算</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依類別用藥筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止痛用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Fentanyl.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Midazolam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鎮靜(苯二氮平類)/麻醉前用藥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV/IM/SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">單次(premed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">常與opioid併用做neuroleptanalgesia；可用Flumazenil 0.01 mg/kg IV逆轉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依類別用藥筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止痛用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Midazolam.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Alfaxalone (Alfaxan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻醉誘導劑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手術麻醉(Induction)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IV(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">緩慢推注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,&gt;60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒</t>
     </r>
     <r>
       <rPr>
@@ -766,67 +852,12 @@
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1-4 mcg/kg/h(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">貓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">呼吸抑制、心搏過緩風險；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">速率非本欄計算範圍，需另外換算</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">單次(誘導)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">犬：premed後2mg/kg、未premed 3mg/kg；貓：約5mg/kg；個體差異大，需 to effect 給藥，年老/重症動物酌減</t>
   </si>
   <si>
     <r>
@@ -894,138 +925,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/Fentanyl.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Midazolam</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鎮靜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">苯二氮平類</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">麻醉前用藥</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">IV/IM/SC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單次</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(premed)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常與</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">opioid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">併用做</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">neuroleptanalgesia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；可用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Flumazenil 0.01 mg/kg IV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逆轉</t>
-    </r>
+      <t xml:space="preserve">/Alfaxalone.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Isoflurane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吸入性麻醉維持</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手術麻醉(Maintenance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吸入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">持續</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠非mg/kg劑量，以吸入濃度(vol%)給予：MAC 犬約1.3%／貓約1.6%；維持濃度約1.5-2.5%</t>
   </si>
   <si>
     <r>
@@ -1093,212 +1012,51 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/Midazolam.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Alfaxalone (Alfaxan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麻醉誘導劑</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術麻醉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Induction)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IV(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">緩慢推注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,&gt;60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">秒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單次</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">誘導</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">犬：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">premed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2mg/kg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、未</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">premed 3mg/kg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；貓：約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5mg/kg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；個體差異大，需 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">to effect </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">給藥，年老</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t xml:space="preserve">/Isoflurane.md</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Panoquell-CA1 (Fuzapladib sodium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">免疫調節劑(LFA-1抑制劑)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住院(急性胰臟炎，僅限犬)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV bolus (15秒-1分鐘推注)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SID x 3天(連續三天)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">僅犬適用(非貓)；常見副作用：厭食、消化道症狀、呼吸道症狀、肝病變、黃疸；蛋白結合率高，併用其他高蛋白結合藥物需留意；FDA為conditional approval階段</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">藥物筆記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1308,31 +1066,11 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重症動物酌減</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
+        <color rgb="FF1155CC"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依類別用藥筆記</t>
     </r>
     <r>
       <rPr>
@@ -1351,240 +1089,17 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">依類別用藥筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止痛用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Alfaxalone.md</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Isoflurane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吸入性麻醉維持</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手術麻醉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Maintenance)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">吸入</t>
-  </si>
-  <si>
-    <t xml:space="preserve">持續</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">⚠非</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mg/kg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">劑量，以吸入濃度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(vol%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">給予：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MAC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">犬約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／貓約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；維持濃度約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.5-2.5%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">藥物筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">依類別用藥筆記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止痛用藥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Isoflurane.md</t>
+      <t xml:space="preserve">腸胃用藥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Panoquell-CA1_Fuzapladib.md</t>
     </r>
   </si>
   <si>
@@ -1877,12 +1392,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00&quot; mg&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; mg&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1980,17 +1494,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="13"/>
       <name val="Noto Sans CJK SC"/>
@@ -2067,7 +1570,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2116,19 +1619,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2388,7 +1903,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -2744,14 +2259,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D13" s="8" t="n">
@@ -2763,32 +2278,32 @@
       <c r="F13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="9" t="n">
         <f aca="false">$B$1*D13</f>
         <v>0.009</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="9" t="n">
         <f aca="false">$B$1*E13</f>
         <v>0.0225</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="10" t="s">
         <v>68</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="7" t="s">
         <v>66</v>
       </c>
       <c r="D14" s="8" t="n">
@@ -2800,32 +2315,32 @@
       <c r="F14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="9" t="n">
         <f aca="false">$B$1*D14</f>
         <v>0.45</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="9" t="n">
         <f aca="false">$B$1*E14</f>
         <v>1.8</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="10" t="s">
         <v>74</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="8" t="n">
@@ -2837,32 +2352,32 @@
       <c r="F15" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="9" t="n">
         <f aca="false">$B$1*D15</f>
         <v>4.5</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="9" t="n">
         <f aca="false">$B$1*E15</f>
         <v>22.5</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="10" t="s">
         <v>81</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D16" s="8" t="n">
@@ -2871,25 +2386,62 @@
       <c r="E16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="9" t="n">
         <f aca="false">$B$1*D16</f>
         <v>0</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="9" t="n">
         <f aca="false">$B$1*E16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="10" t="s">
         <v>88</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <f aca="false">$B$1*D17</f>
+        <v>1.8</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <f aca="false">$B$1*E17</f>
+        <v>1.8</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2915,36 +2467,36 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>90</v>
+      <c r="A1" s="18" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16"/>
+      <c r="A2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>91</v>
+      <c r="A3" s="19" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>92</v>
+      <c r="A4" s="19" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>93</v>
+      <c r="A5" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>94</v>
+      <c r="A6" s="19" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>95</v>
+      <c r="A7" s="19" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
